--- a/student information.xlsx
+++ b/student information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Michael\Documents\RESEARCH CODE (DONOTOPEN)\webportal project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AB1019-89DC-4D59-B715-3D4587E18897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E4CEB2-3BA2-468D-8766-0EF8FC088B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="125">
   <si>
     <t>LRN</t>
   </si>
@@ -394,13 +394,7 @@
     <t>11 Antlia</t>
   </si>
   <si>
-    <t xml:space="preserve">Renecycle Bilat </t>
-  </si>
-  <si>
-    <t>Butterbonia Otin</t>
-  </si>
-  <si>
-    <t>11 Wisdom</t>
+    <t>Water Fire</t>
   </si>
 </sst>
 </file>
@@ -779,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
@@ -888,32 +882,32 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>112234567891</v>
+        <v>112233445577</v>
       </c>
       <c r="B10" t="s">
         <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>112233456789</v>
+        <v>119874160342</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>119874160342</v>
+        <v>119874131178</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
@@ -921,10 +915,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>119874131178</v>
+        <v>119886150058</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
@@ -932,10 +926,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>119886150058</v>
+        <v>119787150122</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
@@ -943,10 +937,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>119787150122</v>
+        <v>119989160318</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
@@ -954,10 +948,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>119989160318</v>
+        <v>404491160093</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -965,10 +959,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>404491160093</v>
+        <v>118967150018</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
@@ -976,10 +970,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>118967150018</v>
+        <v>119485150136</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
@@ -987,10 +981,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>119485150136</v>
+        <v>119880150528</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -998,10 +992,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>119880150528</v>
+        <v>119886150228</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
@@ -1009,10 +1003,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>119886150228</v>
+        <v>120197150018</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -1020,21 +1014,21 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>120197150018</v>
+        <v>119918150018</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>119918150018</v>
+        <v>119874150285</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
         <v>87</v>
@@ -1042,21 +1036,21 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>119874150285</v>
+        <v>119913150058</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>119913150058</v>
+        <v>119893150014</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
         <v>88</v>
@@ -1064,10 +1058,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>119893150014</v>
+        <v>119868150119</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>88</v>
@@ -1075,10 +1069,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>119868150119</v>
+        <v>119793150003</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>88</v>
@@ -1086,10 +1080,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>119793150003</v>
+        <v>119874160453</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>88</v>
@@ -1097,32 +1091,32 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>119874160453</v>
+        <v>119882150204</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>119882150204</v>
+        <v>119874150266</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>119874150266</v>
+        <v>119886150042</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
         <v>88</v>
@@ -1130,21 +1124,21 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>119886150042</v>
+        <v>119880150678</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>119880150678</v>
+        <v>132424150032</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
         <v>89</v>
@@ -1152,10 +1146,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>132424150032</v>
+        <v>447569150050</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34" t="s">
         <v>89</v>
@@ -1163,43 +1157,43 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>447569150050</v>
+        <v>119893150570</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>119893150570</v>
+        <v>1190552150001</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>1190552150001</v>
+        <v>119893160043</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>119893160043</v>
+        <v>119893150223</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
         <v>89</v>
@@ -1207,10 +1201,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>119893150223</v>
+        <v>119145150009</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
         <v>89</v>
@@ -1218,21 +1212,21 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>119145150009</v>
+        <v>119930150133</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>119930150133</v>
+        <v>119918150015</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
         <v>88</v>
@@ -1240,32 +1234,32 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>119918150015</v>
+        <v>119925150195</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>119925150195</v>
+        <v>119874140564</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>119874140564</v>
+        <v>119874150241</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
         <v>89</v>
@@ -1273,32 +1267,32 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>119874150241</v>
+        <v>119766160007</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>119766160007</v>
+        <v>119913150226</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>119913150226</v>
+        <v>119871104277</v>
       </c>
       <c r="B47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
         <v>89</v>
@@ -1306,10 +1300,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>119871104277</v>
+        <v>119874150330</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
         <v>89</v>
@@ -1317,21 +1311,21 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>119874150330</v>
+        <v>119915150107</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>119915150107</v>
+        <v>119880150966</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C50" t="s">
         <v>88</v>
@@ -1339,10 +1333,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>119880150966</v>
+        <v>120006160128</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
         <v>88</v>
@@ -1350,21 +1344,21 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>120006160128</v>
+        <v>119919150099</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>119919150099</v>
+        <v>447509150328</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C53" t="s">
         <v>87</v>
@@ -1372,32 +1366,32 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>447509150328</v>
+        <v>119873150081</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C54" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>119873150081</v>
+        <v>125928150010</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>125928150010</v>
+        <v>119931150069</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C56" t="s">
         <v>88</v>
@@ -1405,54 +1399,54 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>119931150069</v>
+        <v>447552150473</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>447552150473</v>
+        <v>404449150097</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>404449150097</v>
+        <v>114750140024</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>114750140024</v>
+        <v>119886150428</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C60" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>119886150428</v>
+        <v>119874150810</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C61" t="s">
         <v>93</v>
@@ -1460,10 +1454,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>119874150810</v>
+        <v>119907150459</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C62" t="s">
         <v>93</v>
@@ -1471,10 +1465,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>119907150459</v>
+        <v>119913150051</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C63" t="s">
         <v>93</v>
@@ -1482,10 +1476,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>119913150051</v>
+        <v>119874150569</v>
       </c>
       <c r="B64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C64" t="s">
         <v>93</v>
@@ -1493,10 +1487,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>119874150569</v>
+        <v>119893150606</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C65" t="s">
         <v>93</v>
@@ -1504,10 +1498,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>119893150606</v>
+        <v>119874150856</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
         <v>93</v>
@@ -1515,10 +1509,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>119874150856</v>
+        <v>119873150059</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C67" t="s">
         <v>93</v>
@@ -1526,87 +1520,87 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>119873150059</v>
+        <v>447546150048</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C68" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>447546150048</v>
+        <v>119874160455</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>119874160455</v>
+        <v>119915150326</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>119915150326</v>
+        <v>119874150674</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>119874150674</v>
+        <v>119868150164</v>
       </c>
       <c r="B72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C72" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>119868150164</v>
+        <v>119880150542</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>119880150542</v>
+        <v>119880140706</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>119880140706</v>
+        <v>119879150071</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C75" t="s">
         <v>93</v>
@@ -1614,43 +1608,43 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>119879150071</v>
+        <v>119098150038</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C76" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>119098150038</v>
+        <v>119871160593</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>119871160593</v>
+        <v>119287150034</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>119287150034</v>
+        <v>119893140975</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
         <v>90</v>
@@ -1658,43 +1652,43 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>119893140975</v>
+        <v>119874150554</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C80" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>119874150554</v>
+        <v>117205150013</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>117205150013</v>
+        <v>119901160299</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C82" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>119901160299</v>
+        <v>447509150275</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
         <v>91</v>
@@ -1702,65 +1696,65 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>447509150275</v>
+        <v>119901150437</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>119901150437</v>
+        <v>119881150079</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>119881150079</v>
+        <v>119874150566</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>119874150566</v>
+        <v>119869150058</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>119869150058</v>
+        <v>119880150680</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C88" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>119880150680</v>
+        <v>119879160105</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C89" t="s">
         <v>91</v>
@@ -1768,10 +1762,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>119879160105</v>
+        <v>404437150046</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C90" t="s">
         <v>91</v>
@@ -1779,10 +1773,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>404437150046</v>
+        <v>119881150023</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C91" t="s">
         <v>91</v>
@@ -1790,10 +1784,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>119881150023</v>
+        <v>11988260181</v>
       </c>
       <c r="B92" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C92" t="s">
         <v>91</v>
@@ -1801,10 +1795,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>11988260181</v>
+        <v>119930150021</v>
       </c>
       <c r="B93" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C93" t="s">
         <v>91</v>
@@ -1812,10 +1806,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>119930150021</v>
+        <v>119893150001</v>
       </c>
       <c r="B94" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C94" t="s">
         <v>91</v>
@@ -1823,10 +1817,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>119893150001</v>
+        <v>119869150050</v>
       </c>
       <c r="B95" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C95" t="s">
         <v>91</v>
@@ -1834,10 +1828,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>119869150050</v>
+        <v>119873150062</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C96" t="s">
         <v>91</v>
@@ -1845,10 +1839,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>119873150062</v>
+        <v>119901150418</v>
       </c>
       <c r="B97" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C97" t="s">
         <v>91</v>
@@ -1856,65 +1850,65 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>119901150418</v>
+        <v>119874150671</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C98" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>119874150671</v>
+        <v>119874150141</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>119874150141</v>
+        <v>118837150032</v>
       </c>
       <c r="B100" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C100" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>118837150032</v>
+        <v>404462150148</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C101" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>404462150148</v>
+        <v>404471150140</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>404471150140</v>
+        <v>119919150044</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C103" t="s">
         <v>123</v>
@@ -1922,10 +1916,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>119919150044</v>
+        <v>120006150250</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C104" t="s">
         <v>123</v>
@@ -1933,65 +1927,65 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>120006150250</v>
+        <v>119880160050</v>
       </c>
       <c r="B105" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C105" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>119880160050</v>
+        <v>119868150310</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C106" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>119868150310</v>
+        <v>119882150108</v>
       </c>
       <c r="B107" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C107" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>119882150108</v>
+        <v>119263150023</v>
       </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>119263150023</v>
+        <v>119874150548</v>
       </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C109" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>119874150548</v>
+        <v>119868150134</v>
       </c>
       <c r="B110" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C110" t="s">
         <v>123</v>
@@ -1999,34 +1993,23 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>119868150134</v>
+        <v>119919140079</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>119919140079</v>
+        <v>119881150064</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C112" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>119881150064</v>
-      </c>
-      <c r="B113" t="s">
-        <v>122</v>
-      </c>
-      <c r="C113" t="s">
         <v>123</v>
       </c>
     </row>
